--- a/data/marchandises.xlsx
+++ b/data/marchandises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isen\PycharmProjects\Projet_Recherche_Operationnelle\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E094A6-A05F-498F-B28A-30545FAF39B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6F5B82-B252-48F1-AB56-CC7142143B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" xr2:uid="{747BF9E9-3A72-458F-A127-A35EA2613B7B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{747BF9E9-3A72-458F-A127-A35EA2613B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
   <si>
     <t>Longueur</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Designation</t>
+  </si>
+  <si>
+    <t>Retournable</t>
   </si>
 </sst>
 </file>
@@ -548,13 +551,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443758D7-9C7F-4D86-A3F8-4CA75AB87BE6}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -570,8 +573,11 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -587,8 +593,11 @@
       <c r="E2">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -604,8 +613,11 @@
       <c r="E3">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -621,8 +633,11 @@
       <c r="E4">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -638,8 +653,11 @@
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -655,8 +673,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -672,8 +693,11 @@
       <c r="E7">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -689,8 +713,11 @@
       <c r="E8">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -706,8 +733,11 @@
       <c r="E9">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -723,8 +753,11 @@
       <c r="E10">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -740,8 +773,11 @@
       <c r="E11">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -757,8 +793,11 @@
       <c r="E12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -774,8 +813,11 @@
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -791,8 +833,11 @@
       <c r="E14">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -808,8 +853,11 @@
       <c r="E15">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -825,8 +873,11 @@
       <c r="E16">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -842,8 +893,11 @@
       <c r="E17">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -859,8 +913,11 @@
       <c r="E18">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -876,8 +933,11 @@
       <c r="E19">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -893,8 +953,11 @@
       <c r="E20">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -910,8 +973,11 @@
       <c r="E21">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -927,8 +993,11 @@
       <c r="E22">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -944,8 +1013,11 @@
       <c r="E23">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -961,8 +1033,11 @@
       <c r="E24">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -978,8 +1053,11 @@
       <c r="E25">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -995,8 +1073,11 @@
       <c r="E26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1012,8 +1093,11 @@
       <c r="E27">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1029,8 +1113,11 @@
       <c r="E28">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1046,8 +1133,11 @@
       <c r="E29">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1063,8 +1153,11 @@
       <c r="E30">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1080,8 +1173,11 @@
       <c r="E31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1097,8 +1193,11 @@
       <c r="E32">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1114,8 +1213,11 @@
       <c r="E33">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1131,8 +1233,11 @@
       <c r="E34">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1148,8 +1253,11 @@
       <c r="E35">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1165,8 +1273,11 @@
       <c r="E36">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1182,8 +1293,11 @@
       <c r="E37">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1199,8 +1313,11 @@
       <c r="E38">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1216,8 +1333,11 @@
       <c r="E39">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1233,8 +1353,11 @@
       <c r="E40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1250,8 +1373,11 @@
       <c r="E41">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1267,8 +1393,11 @@
       <c r="E42">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1284,8 +1413,11 @@
       <c r="E43">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1301,8 +1433,11 @@
       <c r="E44">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1318,8 +1453,11 @@
       <c r="E45">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1335,8 +1473,11 @@
       <c r="E46">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1352,8 +1493,11 @@
       <c r="E47">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1369,8 +1513,11 @@
       <c r="E48">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1386,8 +1533,11 @@
       <c r="E49">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1403,8 +1553,11 @@
       <c r="E50">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1420,8 +1573,11 @@
       <c r="E51">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1437,8 +1593,11 @@
       <c r="E52">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1454,8 +1613,11 @@
       <c r="E53">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1471,8 +1633,11 @@
       <c r="E54">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1488,8 +1653,11 @@
       <c r="E55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1505,8 +1673,11 @@
       <c r="E56">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1522,8 +1693,11 @@
       <c r="E57">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1539,8 +1713,11 @@
       <c r="E58">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1556,8 +1733,11 @@
       <c r="E59">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1573,8 +1753,11 @@
       <c r="E60">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1590,8 +1773,11 @@
       <c r="E61">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1607,8 +1793,11 @@
       <c r="E62">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1624,8 +1813,11 @@
       <c r="E63">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1641,8 +1833,11 @@
       <c r="E64">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1658,8 +1853,11 @@
       <c r="E65">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1675,8 +1873,11 @@
       <c r="E66">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1692,8 +1893,11 @@
       <c r="E67">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1709,8 +1913,11 @@
       <c r="E68">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1726,8 +1933,11 @@
       <c r="E69">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1743,8 +1953,11 @@
       <c r="E70">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1760,8 +1973,11 @@
       <c r="E71">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1777,8 +1993,11 @@
       <c r="E72">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1794,8 +2013,11 @@
       <c r="E73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1811,8 +2033,11 @@
       <c r="E74">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1828,8 +2053,11 @@
       <c r="E75">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1845,8 +2073,11 @@
       <c r="E76">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1862,8 +2093,11 @@
       <c r="E77">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1879,8 +2113,11 @@
       <c r="E78">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1896,8 +2133,11 @@
       <c r="E79">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1913,8 +2153,11 @@
       <c r="E80">
         <v>2.2999999999999998</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1930,8 +2173,11 @@
       <c r="E81">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1947,8 +2193,11 @@
       <c r="E82">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1964,8 +2213,11 @@
       <c r="E83">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1981,8 +2233,11 @@
       <c r="E84">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1998,8 +2253,11 @@
       <c r="E85">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2015,8 +2273,11 @@
       <c r="E86">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2032,8 +2293,11 @@
       <c r="E87">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2049,8 +2313,11 @@
       <c r="E88">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2066,8 +2333,11 @@
       <c r="E89">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2083,8 +2353,11 @@
       <c r="E90">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2100,8 +2373,11 @@
       <c r="E91">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2117,8 +2393,11 @@
       <c r="E92">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2134,8 +2413,11 @@
       <c r="E93">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2151,8 +2433,11 @@
       <c r="E94">
         <v>1.9</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2168,8 +2453,11 @@
       <c r="E95">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2185,8 +2473,11 @@
       <c r="E96">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2202,8 +2493,11 @@
       <c r="E97">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2219,8 +2513,11 @@
       <c r="E98">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2236,8 +2533,11 @@
       <c r="E99">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2253,8 +2553,11 @@
       <c r="E100">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2269,6 +2572,9 @@
       </c>
       <c r="E101">
         <v>1.3</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
